--- a/data/UPDATED Prediction model elements 9-23-20.xlsx
+++ b/data/UPDATED Prediction model elements 9-23-20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lilybessette/BWH_DoPE/bwh-pharmacoepi-roybal/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8721E5F5-1AB7-DA4B-BD47-2DFE54B77C26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21115215-6697-4546-AB61-4966249015B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="620" yWindow="2220" windowWidth="27700" windowHeight="14800" xr2:uid="{C2F9FED0-CC6C-471D-BFDB-D24CB578A8DE}"/>
+    <workbookView xWindow="6780" yWindow="1740" windowWidth="27700" windowHeight="14800" xr2:uid="{C2F9FED0-CC6C-471D-BFDB-D24CB578A8DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
